--- a/data/90_day_journey.xlsx
+++ b/data/90_day_journey.xlsx
@@ -829,8 +829,7 @@
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>يعني إيه ما لا يسع المسلم جهله؟
-ابن عبد البر قال إيه عن الفرائض اللي لازم كل مسلم يعرفها؟
-مشروع الكتاب ده معمول على كام مرحلة، وكل مرحلة لمين؟</t>
+ابن عبد البر قال إيه عن الفرائض اللي لازم كل مسلم يعرفها؟</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
